--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_2_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_2_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>437338.2504890294</v>
+        <v>440621.5385695739</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.2446352034</v>
+        <v>925399.3994514376</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422528</v>
+        <v>18327015.93006068</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5669203.62085166</v>
+        <v>5669319.084475419</v>
       </c>
     </row>
     <row r="11">
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>102.2970636939287</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -691,31 +691,31 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y2" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="3">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7084989883157</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D3" t="n">
         <v>147.4450655646388</v>
@@ -740,16 +740,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>145.8717589483932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>39.82778746869523</v>
+        <v>39.82778746869526</v>
       </c>
       <c r="J4" t="n">
         <v>93.35918011667277</v>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C5" t="n">
-        <v>58.36784392556159</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>9.234466016111838</v>
       </c>
       <c r="J5" t="n">
         <v>11.94928935461252</v>
@@ -928,19 +928,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T5" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>145.3912560091964</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D6" t="n">
         <v>147.4450655646388</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>17.55829564281238</v>
+        <v>39.82778746869526</v>
       </c>
       <c r="J7" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K7" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1132,19 +1132,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>220.8569218604367</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,22 +1165,22 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>21.18375537072436</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>145.3912560091964</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D9" t="n">
         <v>147.4450655646388</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>22.03399177268427</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>80.33470701582003</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H11" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I11" t="n">
-        <v>80.30783249471889</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1436,31 +1436,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>32.88972338563897</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1487,19 +1487,19 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>104.7383832473596</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1609,16 +1609,16 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1645,22 +1645,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.234466016111835</v>
       </c>
       <c r="W14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>172.7084989883157</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D15" t="n">
         <v>147.4450655646388</v>
@@ -1691,7 +1691,7 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>84.91820125737713</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>17.55829564281238</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
@@ -1852,10 +1852,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1882,16 +1882,16 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>70.31713328017405</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>241</v>
+        <v>120.9273370453295</v>
       </c>
       <c r="V17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1958,28 +1958,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
-        <v>232.8005871494253</v>
+        <v>147.9845033927267</v>
       </c>
       <c r="W18" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>29.75784556612239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2049,10 +2049,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W19" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2071,28 +2071,28 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>241</v>
+        <v>212.285385643442</v>
       </c>
       <c r="D20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.252730413754638</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2153,16 +2153,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2204,19 +2204,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
-        <v>99.5675804066406</v>
+        <v>35.40726547353844</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2368,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="24">
@@ -2387,22 +2387,22 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>89.94022315340511</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>18.617696580776</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2438,19 +2438,19 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
         <v>205.6826957773044</v>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2545,28 +2545,28 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>52.42556848774763</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>190.3328114308862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2621,16 +2621,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.30942629682288</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2675,19 +2675,19 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>69.03881051849277</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2861,19 +2861,19 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>106.0644964958682</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>29.84813499229548</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2949,58 +2949,58 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3016,25 +3016,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>241</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3079,10 +3079,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3101,19 +3101,19 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>91.00042563158644</v>
+        <v>65.28337874243276</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3143,16 +3143,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3161,10 +3161,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -3256,19 +3256,19 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>52.42556848774752</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3298,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3353,7 +3353,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3380,25 +3380,25 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
-        <v>106.0684519266511</v>
+        <v>35.40726547353844</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3493,10 +3493,10 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>62.40368205885025</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3505,10 +3505,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H38" t="n">
-        <v>241</v>
+        <v>102.3382270926889</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3535,19 +3535,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3617,28 +3617,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>23.94690236953673</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>29.79900896488263</v>
       </c>
     </row>
     <row r="40">
@@ -3690,13 +3690,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3711,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3772,31 +3772,31 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>241</v>
+        <v>212.285385643442</v>
       </c>
       <c r="W41" t="n">
-        <v>58.36784392556159</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="42">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3818,19 +3818,19 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>50.05769526855308</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>21.91366464565078</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3866,10 +3866,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
@@ -3942,13 +3942,13 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3973,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>23.7861416288039</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H44" t="n">
-        <v>241</v>
+        <v>114.9581870864144</v>
       </c>
       <c r="I44" t="n">
         <v>210.4758895704059</v>
@@ -4012,7 +4012,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S44" t="n">
         <v>209.0200695862453</v>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4046,22 +4046,22 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C45" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>145.0692123933839</v>
+        <v>29.89893342618437</v>
       </c>
       <c r="G45" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4091,28 +4091,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y45" t="n">
-        <v>53.93787800408713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>122.6103673676048</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C2" t="n">
-        <v>122.6103673676048</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D2" t="n">
-        <v>122.6103673676048</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E2" t="n">
-        <v>122.6103673676048</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F2" t="n">
-        <v>122.6103673676048</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G2" t="n">
-        <v>122.6103673676048</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q2" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R2" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S2" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T2" t="n">
-        <v>366.0447108019482</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U2" t="n">
-        <v>366.0447108019482</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V2" t="n">
-        <v>366.0447108019482</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W2" t="n">
-        <v>366.0447108019482</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X2" t="n">
-        <v>366.0447108019482</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y2" t="n">
-        <v>122.6103673676048</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>648.4394519209488</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C3" t="n">
-        <v>473.9864226398218</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D3" t="n">
-        <v>325.0520129785705</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E3" t="n">
-        <v>165.814557973115</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F3" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G3" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I3" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L3" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M3" t="n">
-        <v>257.87</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N3" t="n">
-        <v>496.46</v>
+        <v>712.019119383956</v>
       </c>
       <c r="O3" t="n">
-        <v>735.0500000000001</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P3" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y3" t="n">
-        <v>816.6547889410169</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I4" t="n">
-        <v>113.5822021380533</v>
+        <v>113.583345248266</v>
       </c>
       <c r="J4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>90.30740735371123</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="C5" t="n">
-        <v>31.34998924708335</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="D5" t="n">
-        <v>31.34998924708335</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="E5" t="n">
-        <v>31.34998924708335</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="F5" t="n">
-        <v>31.34998924708335</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="G5" t="n">
-        <v>31.34998924708335</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="H5" t="n">
-        <v>31.34998924708335</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="I5" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R5" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S5" t="n">
-        <v>802.5254372164702</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T5" t="n">
-        <v>577.1760942223981</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="U5" t="n">
-        <v>333.7417507880547</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="V5" t="n">
-        <v>333.7417507880547</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="W5" t="n">
-        <v>333.7417507880547</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="X5" t="n">
-        <v>333.7417507880547</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="Y5" t="n">
-        <v>90.30740735371123</v>
+        <v>527.5764290961142</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C6" t="n">
-        <v>817.1401454452562</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D6" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E6" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F6" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G6" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H6" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I6" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L6" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M6" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N6" t="n">
-        <v>726.4231058683491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O6" t="n">
-        <v>894.6054414866707</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P6" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I7" t="n">
-        <v>136.0766383258138</v>
+        <v>113.583345248266</v>
       </c>
       <c r="J7" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C8" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D8" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E8" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F8" t="n">
-        <v>730.820584772746</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G8" t="n">
-        <v>487.3862413384025</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H8" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I8" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R8" t="n">
-        <v>953.9083846317729</v>
+        <v>942.6594228129348</v>
       </c>
       <c r="S8" t="n">
-        <v>953.9083846317729</v>
+        <v>731.528039392485</v>
       </c>
       <c r="T8" t="n">
-        <v>953.9083846317729</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="U8" t="n">
-        <v>953.9083846317729</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="V8" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W8" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X8" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y8" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C9" t="n">
-        <v>817.1401454452562</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D9" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E9" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F9" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G9" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H9" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L9" t="n">
-        <v>249.2431058683491</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M9" t="n">
-        <v>487.8331058683492</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N9" t="n">
-        <v>726.4231058683491</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O9" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>151.0633604548096</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q10" t="n">
-        <v>64.03099353390618</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>587.2677095906251</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="C11" t="n">
-        <v>587.2677095906251</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="D11" t="n">
-        <v>587.2677095906251</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E11" t="n">
-        <v>587.2677095906251</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F11" t="n">
-        <v>587.2677095906251</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="G11" t="n">
-        <v>343.8333661562817</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H11" t="n">
-        <v>100.3990227219383</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R11" t="n">
-        <v>812.6170525846973</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S11" t="n">
-        <v>812.6170525846973</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="T11" t="n">
-        <v>587.2677095906251</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="U11" t="n">
-        <v>587.2677095906251</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="V11" t="n">
-        <v>587.2677095906251</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="W11" t="n">
-        <v>587.2677095906251</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="X11" t="n">
-        <v>587.2677095906251</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="Y11" t="n">
-        <v>587.2677095906251</v>
+        <v>587.3248651012614</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>795.7846629799319</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C12" t="n">
-        <v>621.3316336988049</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D12" t="n">
-        <v>472.3972240375537</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E12" t="n">
-        <v>313.1597690320982</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F12" t="n">
-        <v>166.6252110589831</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G12" t="n">
-        <v>133.4032682452064</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>19.28</v>
+        <v>74.24228005117135</v>
       </c>
       <c r="L12" t="n">
-        <v>249.2431058683491</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M12" t="n">
-        <v>487.8331058683492</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N12" t="n">
-        <v>726.4231058683491</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O12" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S12" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T12" t="n">
-        <v>964</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U12" t="n">
-        <v>964</v>
+        <v>360.2295980564601</v>
       </c>
       <c r="V12" t="n">
-        <v>964</v>
+        <v>125.0774898247174</v>
       </c>
       <c r="W12" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X12" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y12" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I13" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>720.5656565656566</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="C14" t="n">
-        <v>477.1313131313132</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="D14" t="n">
-        <v>477.1313131313132</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="E14" t="n">
-        <v>477.1313131313132</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F14" t="n">
-        <v>477.1313131313132</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G14" t="n">
-        <v>233.6969696969697</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H14" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I14" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S14" t="n">
-        <v>964</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T14" t="n">
-        <v>964</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="U14" t="n">
-        <v>964</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="V14" t="n">
-        <v>964</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="W14" t="n">
-        <v>720.5656565656566</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="X14" t="n">
-        <v>720.5656565656566</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="Y14" t="n">
-        <v>720.5656565656566</v>
+        <v>31.35113235729608</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C15" t="n">
-        <v>789.546970718873</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D15" t="n">
-        <v>640.6125610576217</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E15" t="n">
-        <v>481.3751060521662</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F15" t="n">
-        <v>334.8405480790512</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G15" t="n">
-        <v>196.1097226616668</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H15" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L15" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M15" t="n">
-        <v>257.87</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N15" t="n">
-        <v>496.46</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O15" t="n">
-        <v>735.0500000000001</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P15" t="n">
-        <v>917.693477613351</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I16" t="n">
-        <v>136.0766383258138</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J16" t="n">
-        <v>41.77443618776046</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="C17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="D17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="E17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="F17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="G17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="H17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I17" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R17" t="n">
-        <v>802.5254372164702</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S17" t="n">
-        <v>731.498029862759</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T17" t="n">
-        <v>506.1486868686869</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U17" t="n">
-        <v>262.7143434343434</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="V17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="W17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="X17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="Y17" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="C18" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="D18" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="E18" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="F18" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="G18" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="H18" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M18" t="n">
-        <v>257.87</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N18" t="n">
-        <v>496.46</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O18" t="n">
-        <v>735.0500000000001</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P18" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S18" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T18" t="n">
-        <v>964</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U18" t="n">
-        <v>735.7763817363891</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V18" t="n">
-        <v>500.6242735046464</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="W18" t="n">
-        <v>257.1899300703029</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="X18" t="n">
-        <v>49.33842986477009</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C20" t="n">
-        <v>509.4342731452067</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D20" t="n">
-        <v>265.9999297108633</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E20" t="n">
-        <v>22.56558627651984</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F20" t="n">
-        <v>22.56558627651984</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G20" t="n">
-        <v>22.56558627651984</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H20" t="n">
-        <v>22.56558627651984</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>22.56558627651984</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>453.4797930517508</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C21" t="n">
-        <v>453.4797930517508</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D21" t="n">
-        <v>304.5453833904995</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E21" t="n">
-        <v>304.5453833904995</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F21" t="n">
-        <v>158.0108254173845</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M21" t="n">
-        <v>487.8331058683492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N21" t="n">
-        <v>726.4231058683491</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O21" t="n">
-        <v>894.6054414866707</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>761.813405358766</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U21" t="n">
-        <v>761.813405358766</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="V21" t="n">
-        <v>761.813405358766</v>
+        <v>298.4948343740486</v>
       </c>
       <c r="W21" t="n">
-        <v>761.813405358766</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="X21" t="n">
-        <v>661.2400918167048</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y21" t="n">
-        <v>453.4797930517508</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="G22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="H22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="I22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L22" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M22" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N22" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y22" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>223.6053543287427</v>
+        <v>467.067986854209</v>
       </c>
       <c r="C23" t="n">
-        <v>223.6053543287427</v>
+        <v>467.067986854209</v>
       </c>
       <c r="D23" t="n">
-        <v>223.6053543287427</v>
+        <v>467.067986854209</v>
       </c>
       <c r="E23" t="n">
-        <v>223.6053543287427</v>
+        <v>467.067986854209</v>
       </c>
       <c r="F23" t="n">
-        <v>223.6053543287427</v>
+        <v>467.067986854209</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>467.067986854209</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W23" t="n">
-        <v>710.4740411974295</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X23" t="n">
-        <v>467.0396977630861</v>
+        <v>710.516763498309</v>
       </c>
       <c r="Y23" t="n">
-        <v>223.6053543287427</v>
+        <v>467.067986854209</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>284.5817395370918</v>
+        <v>346.2587618989155</v>
       </c>
       <c r="C24" t="n">
-        <v>110.1287102559648</v>
+        <v>346.2587618989155</v>
       </c>
       <c r="D24" t="n">
-        <v>110.1287102559648</v>
+        <v>197.3243522376642</v>
       </c>
       <c r="E24" t="n">
-        <v>110.1287102559648</v>
+        <v>38.08689723220868</v>
       </c>
       <c r="F24" t="n">
-        <v>110.1287102559648</v>
+        <v>38.08689723220868</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>38.08689723220868</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>487.8331058683492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N24" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O24" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U24" t="n">
-        <v>735.7763817363891</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V24" t="n">
-        <v>735.7763817363891</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W24" t="n">
-        <v>492.3420383020457</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="X24" t="n">
-        <v>492.3420383020457</v>
+        <v>554.0190606638694</v>
       </c>
       <c r="Y24" t="n">
-        <v>284.5817395370918</v>
+        <v>346.2587618989155</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>761.6530195501136</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="C26" t="n">
-        <v>518.2186761157702</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="D26" t="n">
-        <v>274.7843326814268</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="E26" t="n">
-        <v>274.7843326814268</v>
+        <v>315.6850394389064</v>
       </c>
       <c r="F26" t="n">
-        <v>274.7843326814268</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G26" t="n">
-        <v>274.7843326814268</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>953.9083846318168</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>953.9083846318168</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S26" t="n">
-        <v>953.9083846318168</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T26" t="n">
-        <v>953.9083846318168</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U26" t="n">
-        <v>953.9083846318168</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="V26" t="n">
-        <v>953.9083846318168</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="W26" t="n">
-        <v>953.9083846318168</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="X26" t="n">
-        <v>953.9083846318168</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="Y26" t="n">
-        <v>761.6530195501136</v>
+        <v>559.1338160830064</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>501.9048939478338</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C27" t="n">
-        <v>327.4518646667068</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D27" t="n">
-        <v>178.5174550054555</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>374.6006659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N27" t="n">
-        <v>613.1906659261865</v>
+        <v>712.019119383956</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>761.813405358766</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>761.813405358766</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V27" t="n">
-        <v>761.813405358766</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W27" t="n">
-        <v>518.3790619244226</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X27" t="n">
-        <v>518.3790619244226</v>
+        <v>187.4964801302808</v>
       </c>
       <c r="Y27" t="n">
-        <v>518.3790619244226</v>
+        <v>187.4964801302808</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y29" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.28</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C30" t="n">
-        <v>19.28</v>
+        <v>613.4725238202047</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>464.5381141589534</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M30" t="n">
-        <v>304.1765223866491</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N30" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>933.850368694651</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>933.850368694651</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>933.850368694651</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>705.6267504310401</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V30" t="n">
-        <v>470.4746421992974</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W30" t="n">
-        <v>227.0402987649539</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X30" t="n">
-        <v>227.0402987649539</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.28</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>749.5830303030303</v>
+        <v>467.067986854209</v>
       </c>
       <c r="C32" t="n">
-        <v>749.5830303030303</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="D32" t="n">
-        <v>749.5830303030303</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="E32" t="n">
-        <v>506.1486868686869</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="F32" t="n">
-        <v>506.1486868686869</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="G32" t="n">
-        <v>262.7143434343434</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="H32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S32" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T32" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U32" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V32" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W32" t="n">
-        <v>964</v>
+        <v>710.516763498309</v>
       </c>
       <c r="X32" t="n">
-        <v>964</v>
+        <v>467.067986854209</v>
       </c>
       <c r="Y32" t="n">
-        <v>964</v>
+        <v>467.067986854209</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>224.568757442508</v>
+        <v>380.6929175551172</v>
       </c>
       <c r="C33" t="n">
-        <v>224.568757442508</v>
+        <v>380.6929175551172</v>
       </c>
       <c r="D33" t="n">
-        <v>224.568757442508</v>
+        <v>231.7585078938659</v>
       </c>
       <c r="E33" t="n">
-        <v>224.568757442508</v>
+        <v>231.7585078938659</v>
       </c>
       <c r="F33" t="n">
-        <v>224.568757442508</v>
+        <v>85.22394992075087</v>
       </c>
       <c r="G33" t="n">
-        <v>132.6491355924207</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>304.1765223866491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M33" t="n">
-        <v>304.1765223866491</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N33" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O33" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P33" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>862.8304705528857</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T33" t="n">
-        <v>660.6438759116518</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U33" t="n">
-        <v>432.4202576480408</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="V33" t="n">
-        <v>432.4202576480408</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="W33" t="n">
-        <v>432.4202576480408</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="X33" t="n">
-        <v>224.568757442508</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="Y33" t="n">
-        <v>224.568757442508</v>
+        <v>380.6929175551172</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>506.1486868686869</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="C35" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D35" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="E35" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F35" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R35" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S35" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T35" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U35" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="V35" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="W35" t="n">
-        <v>749.5830303030303</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="X35" t="n">
-        <v>749.5830303030303</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="Y35" t="n">
-        <v>506.1486868686869</v>
+        <v>802.5825927271064</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>284.0326584239705</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C36" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D36" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E36" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F36" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G36" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H36" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L36" t="n">
-        <v>304.1765223866491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M36" t="n">
-        <v>304.1765223866491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N36" t="n">
-        <v>542.7665223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O36" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>862.8304705528857</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U36" t="n">
-        <v>634.6068522892747</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="V36" t="n">
-        <v>634.6068522892747</v>
+        <v>298.4948343740486</v>
       </c>
       <c r="W36" t="n">
-        <v>391.1725088549313</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="X36" t="n">
-        <v>284.0326584239705</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y36" t="n">
-        <v>284.0326584239705</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>569.1827091503538</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="C38" t="n">
-        <v>506.1486868686869</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="D38" t="n">
-        <v>262.7143434343434</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="E38" t="n">
-        <v>262.7143434343434</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="F38" t="n">
-        <v>262.7143434343434</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="G38" t="n">
-        <v>262.7143434343434</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="H38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R38" t="n">
-        <v>812.6170525846973</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S38" t="n">
-        <v>812.6170525846973</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T38" t="n">
-        <v>812.6170525846973</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U38" t="n">
-        <v>569.1827091503538</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="V38" t="n">
-        <v>569.1827091503538</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="W38" t="n">
-        <v>569.1827091503538</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="X38" t="n">
-        <v>569.1827091503538</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="Y38" t="n">
-        <v>569.1827091503538</v>
+        <v>366.1018663125844</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L39" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M39" t="n">
-        <v>304.1765223866491</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N39" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O39" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T39" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U39" t="n">
-        <v>463.0377410900613</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V39" t="n">
-        <v>227.8856328583186</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W39" t="n">
-        <v>227.8856328583186</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X39" t="n">
-        <v>20.03413265278571</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C41" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D41" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O41" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P41" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R41" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S41" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T41" t="n">
-        <v>577.1760942223981</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U41" t="n">
-        <v>333.7417507880547</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V41" t="n">
-        <v>90.30740735371123</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W41" t="n">
-        <v>31.34998924708335</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X41" t="n">
-        <v>31.34998924708335</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y41" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>279.0033345623309</v>
+        <v>69.84447166430675</v>
       </c>
       <c r="C42" t="n">
-        <v>279.0033345623309</v>
+        <v>69.84447166430675</v>
       </c>
       <c r="D42" t="n">
-        <v>279.0033345623309</v>
+        <v>69.84447166430675</v>
       </c>
       <c r="E42" t="n">
-        <v>279.0033345623309</v>
+        <v>69.84447166430675</v>
       </c>
       <c r="F42" t="n">
-        <v>132.4687765892159</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G42" t="n">
-        <v>132.4687765892159</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H42" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I42" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L42" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M42" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N42" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O42" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P42" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R42" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S42" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T42" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U42" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V42" t="n">
-        <v>862.8304705528857</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W42" t="n">
-        <v>862.8304705528857</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="X42" t="n">
-        <v>654.9789703473529</v>
+        <v>277.6047704292607</v>
       </c>
       <c r="Y42" t="n">
-        <v>447.2186715823989</v>
+        <v>69.84447166430675</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>499.3426577769796</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="C44" t="n">
-        <v>499.3426577769796</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="D44" t="n">
-        <v>499.3426577769796</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="E44" t="n">
-        <v>475.3162520913191</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="F44" t="n">
-        <v>475.3162520913191</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="G44" t="n">
-        <v>475.3162520913191</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="H44" t="n">
-        <v>231.8819086569757</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R44" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S44" t="n">
-        <v>742.7770012113231</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T44" t="n">
-        <v>742.7770012113231</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="U44" t="n">
-        <v>499.3426577769796</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="V44" t="n">
-        <v>499.3426577769796</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="W44" t="n">
-        <v>499.3426577769796</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="X44" t="n">
-        <v>499.3426577769796</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="Y44" t="n">
-        <v>499.3426577769796</v>
+        <v>591.4512093066566</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>741.3019579252984</v>
+        <v>49.48208596494442</v>
       </c>
       <c r="C45" t="n">
-        <v>566.8489286441715</v>
+        <v>49.48208596494442</v>
       </c>
       <c r="D45" t="n">
-        <v>417.9145189829202</v>
+        <v>49.48208596494442</v>
       </c>
       <c r="E45" t="n">
-        <v>417.9145189829202</v>
+        <v>49.48208596494442</v>
       </c>
       <c r="F45" t="n">
-        <v>271.3799610098052</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G45" t="n">
-        <v>132.6491355924207</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L45" t="n">
-        <v>19.28</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M45" t="n">
-        <v>257.87</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N45" t="n">
-        <v>473.3719638733197</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O45" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P45" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R45" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S45" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T45" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="U45" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="V45" t="n">
-        <v>964</v>
+        <v>425.5489231905453</v>
       </c>
       <c r="W45" t="n">
-        <v>964</v>
+        <v>425.5489231905453</v>
       </c>
       <c r="X45" t="n">
-        <v>964</v>
+        <v>217.6974229850125</v>
       </c>
       <c r="Y45" t="n">
-        <v>909.5172949453665</v>
+        <v>217.6974229850125</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L46" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M46" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N46" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
   </sheetData>
@@ -7959,10 +7959,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K2" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L2" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M2" t="n">
         <v>449.5135334928325</v>
@@ -8038,22 +8038,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K3" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L3" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M3" t="n">
-        <v>383.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N3" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O3" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P3" t="n">
-        <v>295.1415200271288</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q3" t="n">
         <v>210.0772877358491</v>
@@ -8196,7 +8196,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L5" t="n">
         <v>417.6612145504504</v>
@@ -8275,22 +8275,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K6" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L6" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M6" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N6" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>312.4773915336581</v>
+        <v>242.4075215744184</v>
       </c>
       <c r="P6" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q6" t="n">
         <v>210.0772877358491</v>
@@ -8433,7 +8433,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L8" t="n">
         <v>417.6612145504504</v>
@@ -8512,19 +8512,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L9" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>383.1340339220183</v>
+        <v>303.312501347746</v>
       </c>
       <c r="N9" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O9" t="n">
-        <v>198.0845439578789</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P9" t="n">
         <v>318.4627686399372</v>
@@ -8670,10 +8670,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L11" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M11" t="n">
         <v>449.5135334928325</v>
@@ -8749,22 +8749,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>193.3577389147212</v>
       </c>
       <c r="L12" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M12" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O12" t="n">
-        <v>382.5729051834858</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P12" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q12" t="n">
         <v>139.9817740860215</v>
@@ -8907,7 +8907,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L14" t="n">
         <v>417.6612145504504</v>
@@ -8922,7 +8922,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P14" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M15" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N15" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O15" t="n">
-        <v>383.5962444444444</v>
+        <v>185.8815939223662</v>
       </c>
       <c r="P15" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>186.7560391230408</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9159,7 +9159,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P17" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9229,16 +9229,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>383.1340339220183</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N18" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O18" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P18" t="n">
-        <v>295.1415200271288</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q18" t="n">
         <v>210.0772877358491</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9466,16 +9466,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>368.5691090902119</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>312.4773915336581</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
         <v>210.0772877358491</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,19 +9697,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N24" t="n">
-        <v>186.8300115967677</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
@@ -9870,7 +9870,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P26" t="n">
-        <v>321.742129989281</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9940,19 +9940,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>312.4607459196593</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10177,19 +10177,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>303.2845009208181</v>
+        <v>233.2169876979182</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10411,22 +10411,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>299.7048467786739</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N33" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,7 +10566,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
@@ -10648,19 +10648,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>299.7048467786739</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>372.3417120833333</v>
+        <v>244.7225752110828</v>
       </c>
       <c r="O36" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
         <v>139.9817740860215</v>
@@ -10803,7 +10803,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
@@ -10888,13 +10888,13 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>303.2845009208181</v>
+        <v>303.312501347746</v>
       </c>
       <c r="N39" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O39" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
@@ -11046,7 +11046,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M42" t="n">
-        <v>311.9985353972331</v>
+        <v>368.5691090902119</v>
       </c>
       <c r="N42" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11292,7 +11292,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P44" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q44" t="n">
         <v>212.3149906599047</v>
@@ -11359,22 +11359,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M45" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N45" t="n">
-        <v>349.020463470525</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O45" t="n">
-        <v>383.5962444444444</v>
+        <v>198.1125443848066</v>
       </c>
       <c r="P45" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q45" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -22522,7 +22522,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H2" t="n">
-        <v>237.1777384218384</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I2" t="n">
         <v>210.4758895704059</v>
@@ -22549,31 +22549,31 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V2" t="n">
-        <v>327.7522584701349</v>
+        <v>115.4668728266929</v>
       </c>
       <c r="W2" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X2" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y2" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="3">
@@ -22583,10 +22583,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -22598,16 +22598,16 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -22652,7 +22652,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y3" t="n">
-        <v>59.81093682891111</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="4">
@@ -22741,10 +22741,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C5" t="n">
-        <v>306.9050478454459</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D5" t="n">
         <v>354.683041620683</v>
@@ -22753,7 +22753,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F5" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G5" t="n">
         <v>415.302737515135</v>
@@ -22762,7 +22762,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>201.2414235542941</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -22786,19 +22786,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S5" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -22810,7 +22810,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y5" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="6">
@@ -22823,7 +22823,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>27.31724297911936</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -22920,13 +22920,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I7" t="n">
-        <v>137.8921792844459</v>
+        <v>115.622687458563</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -22990,19 +22990,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>186.0191238812747</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,22 +23023,22 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>128.6853625704253</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V8" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W8" t="n">
         <v>349.240968717413</v>
@@ -23060,7 +23060,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>27.31724297911936</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23184,7 +23184,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>155.2593996044852</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
@@ -23221,7 +23221,7 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D11" t="n">
-        <v>354.683041620683</v>
+        <v>274.3483346048629</v>
       </c>
       <c r="E11" t="n">
         <v>381.9303700722618</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H11" t="n">
-        <v>98.47480211576715</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I11" t="n">
-        <v>130.168057075687</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -23294,31 +23294,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>104.4537937775717</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23345,19 +23345,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>251.6949831609196</v>
+        <v>146.95659991356</v>
       </c>
       <c r="X12" t="n">
         <v>205.7729852034775</v>
@@ -23394,13 +23394,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23421,7 +23421,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S13" t="n">
         <v>224.0165980369723</v>
@@ -23455,7 +23455,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C14" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D14" t="n">
         <v>354.683041620683</v>
@@ -23467,16 +23467,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
-        <v>127.2020021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23503,22 +23503,22 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V14" t="n">
-        <v>327.7522584701349</v>
+        <v>318.5177924540231</v>
       </c>
       <c r="W14" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X14" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y14" t="n">
         <v>386.2379386560536</v>
@@ -23534,7 +23534,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -23549,7 +23549,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>27.31724297911931</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23710,10 +23710,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23740,16 +23740,16 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>138.7029363060713</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>10.3456529078365</v>
+        <v>130.418315862507</v>
       </c>
       <c r="V17" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W17" t="n">
         <v>349.240968717413</v>
@@ -23789,7 +23789,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0.7465913262578567</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>84.81608375669853</v>
       </c>
       <c r="W18" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
-        <v>175.924850211182</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="19">
@@ -23907,10 +23907,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W19" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
         <v>225.7096553890372</v>
@@ -23929,28 +23929,28 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>124.2728917710076</v>
+        <v>152.9875061275656</v>
       </c>
       <c r="D20" t="n">
-        <v>113.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E20" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G20" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>8.69655894085788</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23977,7 +23977,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
         <v>223.0958495641314</v>
@@ -24011,16 +24011,16 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
         <v>112.2354442364965</v>
@@ -24062,19 +24062,19 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
-        <v>106.2054047968369</v>
+        <v>170.365719729939</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24105,7 +24105,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I22" t="n">
-        <v>155.4504749272583</v>
+        <v>22.26350734189029</v>
       </c>
       <c r="J22" t="n">
         <v>93.35918011667277</v>
@@ -24132,7 +24132,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>44.10642379180146</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
         <v>224.0165980369723</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>213.0206367296798</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>8.181203141508689</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -24226,13 +24226,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y23" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="24">
@@ -24245,22 +24245,22 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>47.40329400980552</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>93.61774765572046</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -24296,19 +24296,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -24369,7 +24369,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S25" t="n">
         <v>224.0165980369723</v>
@@ -24378,7 +24378,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24403,28 +24403,28 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F26" t="n">
-        <v>406.8760457417114</v>
+        <v>354.4504772539638</v>
       </c>
       <c r="G26" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H26" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24448,7 +24448,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>209.0200695862453</v>
@@ -24460,7 +24460,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
@@ -24469,7 +24469,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>195.9051272251674</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24479,16 +24479,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>150.2237573530444</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
         <v>145.0692123933839</v>
@@ -24533,19 +24533,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>136.7341746849847</v>
       </c>
       <c r="Y27" t="n">
         <v>205.6826957773044</v>
@@ -24561,7 +24561,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C28" t="n">
-        <v>34.05985351325981</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D28" t="n">
         <v>148.6154730182124</v>
@@ -24603,7 +24603,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q28" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>177.2933913771695</v>
@@ -24618,7 +24618,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
-        <v>252.137643323828</v>
+        <v>205.1127189901543</v>
       </c>
       <c r="W28" t="n">
         <v>286.522998336591</v>
@@ -24637,19 +24637,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>141.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F29" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
         <v>415.302737515135</v>
@@ -24691,7 +24691,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U29" t="n">
         <v>251.3456529078365</v>
@@ -24706,7 +24706,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>173.9651386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24719,19 +24719,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>66.64400249244758</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -24740,7 +24740,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24764,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>70.30969916034765</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
@@ -24773,19 +24773,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -24807,7 +24807,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F31" t="n">
-        <v>12.23408043756322</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
         <v>167.9909793584588</v>
@@ -24858,7 +24858,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W31" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X31" t="n">
         <v>225.7096553890372</v>
@@ -24874,25 +24874,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>170.4610416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
-        <v>98.47480211576715</v>
+        <v>137.1801156868699</v>
       </c>
       <c r="I32" t="n">
         <v>210.4758895704059</v>
@@ -24919,7 +24919,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>149.8691179411497</v>
@@ -24937,10 +24937,10 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X32" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y32" t="n">
         <v>386.2379386560536</v>
@@ -24959,19 +24959,19 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>46.3430915316242</v>
+        <v>72.06013842077788</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25019,10 +25019,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25114,19 +25114,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>365.2728917710076</v>
+        <v>312.84732328326</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F35" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G35" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
@@ -25156,10 +25156,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
@@ -25174,13 +25174,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>136.9681687174131</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="36">
@@ -25193,7 +25193,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
         <v>147.4450655646388</v>
@@ -25211,7 +25211,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
         <v>0.7465913262578567</v>
@@ -25238,25 +25238,25 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
-        <v>99.70453327682635</v>
+        <v>170.365719729939</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25281,7 +25281,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F37" t="n">
-        <v>145.4210480229312</v>
+        <v>12.23408043756322</v>
       </c>
       <c r="G37" t="n">
         <v>167.9909793584588</v>
@@ -25317,7 +25317,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>44.10642379180146</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25351,10 +25351,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>302.8692097121573</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
         <v>381.9303700722618</v>
@@ -25363,10 +25363,10 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H38" t="n">
-        <v>98.47480211576715</v>
+        <v>237.1365750230782</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
@@ -25393,19 +25393,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25451,7 +25451,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25475,28 +25475,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>201.9944797114381</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>175.8836868124217</v>
       </c>
     </row>
     <row r="40">
@@ -25548,13 +25548,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>132.9899077786024</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
         <v>224.0165980369723</v>
@@ -25569,7 +25569,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
@@ -25594,7 +25594,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
@@ -25609,7 +25609,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25630,31 +25630,31 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>86.7522584701349</v>
+        <v>115.4668728266929</v>
       </c>
       <c r="W41" t="n">
-        <v>290.8731247918514</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="42">
@@ -25664,7 +25664,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
         <v>172.7084989883157</v>
@@ -25676,19 +25676,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>95.01151712483079</v>
       </c>
       <c r="G42" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>90.32177959084568</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25712,7 +25712,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
         <v>171.6831711038378</v>
@@ -25724,10 +25724,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25800,13 +25800,13 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X43" t="n">
         <v>225.7096553890372</v>
@@ -25831,16 +25831,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E44" t="n">
-        <v>358.1442284434579</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F44" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H44" t="n">
-        <v>98.47480211576715</v>
+        <v>224.5166150293527</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25870,7 +25870,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -25879,7 +25879,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U44" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25904,22 +25904,22 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E45" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>115.1702789671995</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I45" t="n">
         <v>89.39663285141508</v>
@@ -25949,28 +25949,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T45" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V45" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X45" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>151.7448177732172</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="46">
@@ -26028,7 +26028,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R46" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S46" t="n">
         <v>224.0165980369723</v>
@@ -26043,7 +26043,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W46" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X46" t="n">
         <v>225.7096553890372</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575746</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>490283.0883524074</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575746</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>490283.0883524124</v>
+        <v>490293.0738575743</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>490283.0883524072</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>490283.0883524072</v>
+        <v>490293.0738575746</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575745</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>490283.0883524073</v>
+        <v>490293.0738575744</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="C2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="D2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="E2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="F2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="G2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="H2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="I2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="J2" t="n">
-        <v>108002.2384626071</v>
+        <v>108004.437145366</v>
       </c>
       <c r="K2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="L2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="M2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="N2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="O2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="P2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154773</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910623</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16914.33416026178</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="C4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="D4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="E4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="F4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="G4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="H4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="I4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="J4" t="n">
-        <v>16914.33416026197</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="K4" t="n">
-        <v>16914.33416026178</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="L4" t="n">
-        <v>16914.33416026179</v>
+        <v>16522.45939543528</v>
       </c>
       <c r="M4" t="n">
-        <v>16914.33416026178</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="N4" t="n">
-        <v>16914.33416026178</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="O4" t="n">
-        <v>16914.33416026178</v>
+        <v>16522.45939543529</v>
       </c>
       <c r="P4" t="n">
-        <v>16914.33416026178</v>
+        <v>16522.45939543528</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-37957.13869765574</v>
+        <v>-37568.72254537859</v>
       </c>
       <c r="C6" t="n">
-        <v>42807.50430234421</v>
+        <v>43200.7089861691</v>
       </c>
       <c r="D6" t="n">
-        <v>42807.50430234424</v>
+        <v>43200.70898616911</v>
       </c>
       <c r="E6" t="n">
-        <v>76435.1043023442</v>
+        <v>76828.30898616907</v>
       </c>
       <c r="F6" t="n">
-        <v>76435.10430234423</v>
+        <v>76828.30898616911</v>
       </c>
       <c r="G6" t="n">
-        <v>76435.10430234422</v>
+        <v>76828.3089861691</v>
       </c>
       <c r="H6" t="n">
-        <v>76435.1043023442</v>
+        <v>76828.30898616907</v>
       </c>
       <c r="I6" t="n">
-        <v>76435.10430234419</v>
+        <v>76828.30898616908</v>
       </c>
       <c r="J6" t="n">
-        <v>13378.90030234516</v>
+        <v>13768.36638706284</v>
       </c>
       <c r="K6" t="n">
-        <v>76435.10430234425</v>
+        <v>76828.30898616908</v>
       </c>
       <c r="L6" t="n">
-        <v>76435.1043023442</v>
+        <v>76828.30898616908</v>
       </c>
       <c r="M6" t="n">
-        <v>76435.10430234422</v>
+        <v>76828.30898616907</v>
       </c>
       <c r="N6" t="n">
-        <v>76435.10430234425</v>
+        <v>76828.30898616911</v>
       </c>
       <c r="O6" t="n">
-        <v>76435.10430234422</v>
+        <v>76828.30898616908</v>
       </c>
       <c r="P6" t="n">
-        <v>76435.1043023442</v>
+        <v>76828.30898616908</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,7 +26895,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26907,34 +26907,34 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34617,7 +34617,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L2" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M2" t="n">
         <v>219.1673002655598</v>
@@ -34693,22 +34693,22 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M3" t="n">
-        <v>241</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>161.1671126127986</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q3" t="n">
         <v>70.09551364982758</v>
@@ -34851,13 +34851,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L5" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M5" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N5" t="n">
         <v>207.9338608153932</v>
@@ -34930,22 +34930,22 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L6" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>169.8811470892137</v>
+        <v>99.8112771299739</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q6" t="n">
         <v>70.09551364982758</v>
@@ -35088,7 +35088,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L8" t="n">
         <v>181.8947995804632</v>
@@ -35100,7 +35100,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O8" t="n">
-        <v>150.7019698410586</v>
+        <v>150.7019698410587</v>
       </c>
       <c r="P8" t="n">
         <v>90.5657124162131</v>
@@ -35167,19 +35167,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L9" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>241</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="N9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O9" t="n">
-        <v>55.48829951343442</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P9" t="n">
         <v>184.4883612256069</v>
@@ -35325,7 +35325,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L11" t="n">
         <v>181.8947995804632</v>
@@ -35404,22 +35404,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="L12" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M12" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O12" t="n">
-        <v>239.9766607390413</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35577,7 +35577,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P14" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O15" t="n">
-        <v>241</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="P15" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>46.77426503701921</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35814,7 +35814,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P17" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35884,16 +35884,16 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P18" t="n">
-        <v>161.1671126127986</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q18" t="n">
         <v>70.09551364982758</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,16 +36121,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>169.8811470892137</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
         <v>70.09551364982758</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,19 +36352,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N24" t="n">
-        <v>55.48829951343436</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
@@ -36525,7 +36525,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P26" t="n">
-        <v>90.5091342340115</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36595,19 +36595,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>169.8645014752148</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36832,19 +36832,19 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>161.1504669987997</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37066,22 +37066,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>161.1504669987997</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N33" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37221,7 +37221,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
@@ -37303,19 +37303,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>161.1504669987997</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>241</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="O36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37458,7 +37458,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
@@ -37543,13 +37543,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>161.1504669987997</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="N39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
@@ -37701,7 +37701,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M42" t="n">
-        <v>169.8645014752148</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37938,7 +37938,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M44" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N44" t="n">
         <v>207.9338608153932</v>
@@ -37947,7 +37947,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P44" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38014,22 +38014,22 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N45" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O45" t="n">
-        <v>241</v>
+        <v>55.51629994036219</v>
       </c>
       <c r="P45" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q45" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
